--- a/tables/RatioCompetitiveIntelligence/RatioCompetitiveIntelligence_Verified1.xlsx
+++ b/tables/RatioCompetitiveIntelligence/RatioCompetitiveIntelligence_Verified1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://eliyahuai-my.sharepoint.com/personal/eliyahu_eliyahu_ai/Documents/Desktop/src/perplexityValidator/tables/RatioCompetitiveIntelligence/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F8566EFE-3C82-401E-8F99-5152320F3E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{F8566EFE-3C82-401E-8F99-5152320F3E8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{87A236AE-E551-4DBF-A48C-93D1A68CC396}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1003" windowWidth="21943" windowHeight="12711" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="377" yWindow="377" windowWidth="31783" windowHeight="13054" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -27,569 +27,7 @@
     <author/>
   </authors>
   <commentList>
-    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Cancer-associated fibroblasts selectively expressing FAP comprise up to 90% of the tumor mass in highly desmoplastic cancers, including pancreatic, breast, and colorectal. RTX-1363S has the potential to transform the way we detect and monitor various epithelial-derived cancers."
-Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.cancer.gov/about-cancer/treatment/clinical-trials/search/v?id=NCI-2025-01031, https://jnm.snmjournals.org/content/66/supplement_1/251890</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "RTX-1363S is a highly selective, high affinity FAP inhibitor that will be radiolabeled with copper-64 (Cu-64), a positron-emitting radionuclide with a half-life of 12.7 hr."
-Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "RTX-1363S is a highly selective, high affinity FAP inhibitor that will be radiolabeled with copper-64 (Cu-64), a positron-emitting radionuclide with a half-life of 12.7 hr."
-Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "RTX-1363S is a highly selective, high affinity FAP inhibitor that will be radiolabeled with copper-64 (Cu-64), a positron-emitting radionuclide with a half-life of 12.7 hr."
-Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "This is a multicenter, open-label, prospective Phase 1/2a study to assess safety and tolerability, establish dosimetry and to identify an optimal imaging dose."
-Sources: https://www.cancer.gov/about-cancer/treatment/clinical-trials/search/v?id=NCI-2025-01031</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "This is a multicenter, open-label, prospective Phase 1/2a study to assess safety and tolerability, establish dosimetry and to identify an optimal imaging dose."
-Sources: https://www.cancer.gov/about-cancer/treatment/clinical-trials/search/v?id=NCI-2025-01031</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "The study's results will guide further development of [Cu-64]-labeled RTX-1363S as a FAP-targeted tumor imaging agent."
-Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "No mention of FDA or EMA designations in available sources."
-Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio Therapeutics, in collaboration with Lantheus and PharmaLogic, has dosed the first patient in a phase I study investigating a novel fibroblast activated protein inhibitor (FAPI)-targeted radiopharmaceutical for PET imaging."
-Sources: https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio, in collaboration with Lantheus and PharmaLogic, is currently conducting a Phase I trial evaluating the efficacy of a novel FAP-targeted imaging biomarker, copper-64[Cu-64]-labeled LNTH-1363S (formerly RTX-1363S) for PET imaging in adult healthy volunteers. The company also recently announced a $50M Series B financing which will significantly drive the clinical advancement of Ratio’s first FAP-targeted therapeutic candidate into clinical trials this year."
-Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/, https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio is currently advancing its lead FAP-targeted radiotherapeutic candidate for the treatment of soft tissue sarcoma, with plans to initiate clinical trials in late 2024."
-Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio is developing a technology platform to take advantage of the tumor killing power of the alpha emitter, Actinium-225."
-Sources: https://ratiotx.com/press-release-ratio-therapeutics-launches/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio, in collaboration with Lantheus and PharmaLogic, is currently conducting a Phase I trial evaluating the efficacy of a novel FAP-targeted imaging biomarker, copper-64[Cu-64]-labeled LNTH-1363S (formerly RTX-1363S) for PET imaging in adult healthy volunteers."
-Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio is currently advancing its lead FAP-targeted radiotherapeutic candidate for the treatment of soft tissue sarcoma... Ratio’s technology platform... enables the development of tunable radiopharmaceuticals for therapy and imaging."
-Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/, https://ratiotx.com/press-release-ratio-therapeutics-launches/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "A number of groups have explored 225Ac therapy at preclinical level. One study showed that the effects of treatment with 177Lu-FAPI-46 were relatively slow but lasted longer than those of 225Ac-FAPI-46... Recently, an American group has been looking at 225Ac-FAPI-46 therapy combined with immunotherapy in immunocompetent mice with sarcomas sensitive or resistant to immunotherapy."
-Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "No clinical trial identifier found for Ratio Therapeutics' FAP-α 225Ac radiotherapeutic in soft tissue sarcoma."
-Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "The list focuses on agents in pre-registration through Phase 1 and likely to reach market in 2024-2030. ... Ratio Therapeutics' FAP-α 225Ac Radiotherapeutic is in pre-clinical stage."
-Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820, https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf017/7985571</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "No public information available regarding FDA or EMA designations for Ratio Therapeutics' FAP-α 225Ac Radiotherapeutic."
-Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820, https://jnm.snmjournals.org/content/66/supplement_1/251900</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "No public information available regarding key collaborators or licensees for Ratio Therapeutics' FAP-α 225Ac Radiotherapeutic."
-Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820, https://jnm.snmjournals.org/content/66/supplement_1/251900</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio, in collaboration with Lantheus and PharmaLogic, is currently conducting a Phase I trial evaluating the efficacy of a novel FAP-targeted imaging biomarker... The company also recently announced a $50M Series B financing which will significantly drive the clinical advancement of Ratio’s first FAP-targeted therapeutic candidate into clinical trials this year."
-Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/, https://ratiotx.com/press-release-ratio-therapeutics-launches/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Together, we aim to develop a best-in-class therapy in the fight against SSTR2-expressing tumors."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio Therapeutics has inked an exclusive worldwide agreement potentially worth $745M with Novartis Pharma AG. The collaboration leverages Ratio’s radioligand therapy discovery and development expertise as well as its technology platforms for the development of a Somatostatin Receptor 2 (SSTR2) radiotherapeutic candidate for cancer."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
-Sources: https://ratiotx.com/2024/11/18/november-18th-2024-ratio-enters-license-and-collaboration-agreement-with-novartis-for-sstr2-targeting-radiotherapeutic-candidate/, https://firstwordpharma.com/story/5958720</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
-Sources: https://ratiotx.com/2024/11/18/november-18th-2024-ratio-enters-license-and-collaboration-agreement-with-novartis-for-sstr2-targeting-radiotherapeutic-candidate/, https://firstwordpharma.com/story/5958720</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio Therapeutics has inked an exclusive worldwide agreement potentially worth $745M with Novartis Pharma AG. The collaboration leverages Ratio’s radioligand therapy discovery and development expertise as well as its technology platforms for the development of a Somatostatin Receptor 2 (SSTR2) radiotherapeutic candidate for cancer. Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate. Novartis will assume responsibility for all remaining development, manufacturing, and commercialization activities."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "No public information available regarding FDA or EMA designations for this specific SSTR2-targeted radiotherapeutic from Ratio Therapeutics/Novartis."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio Therapeutics has inked an exclusive worldwide agreement potentially worth $745M with Novartis Pharma AG. The collaboration leverages Ratio’s radioligand therapy discovery and development expertise as well as its technology platforms for the development of a Somatostatin Receptor 2 (SSTR2) radiotherapeutic candidate for cancer."
-Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate. Novartis will assume responsibility for all remaining development, manufacturing, and commercialization activities. Under the terms of the agreement, Ratio will receive combined upfront and potential milestone payments up to $745m, and is eligible to receive tiered royalty payments."
-Sources: https://ratiotx.com/2024/11/18/november-18th-2024-ratio-enters-license-and-collaboration-agreement-with-novartis-for-sstr2-targeting-radiotherapeutic-candidate/, https://firstwordpharma.com/story/5958720</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "This clinical trial is studying a new imaging technique that uses a special marker to help doctors monitor how well immunotherapy is working for patients with advanced solid tumors... The trial will compare this new imaging method, which targets a protein called Granzyme B (GZMB), with the current standard imaging technique, 18F-FDG PET/CT."
-Sources: https://clinconnect.io/trials/NCT06916442</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "CytoSite Bio is developing novel radiopharmaceuticals that enable the quantification and modulation of immune activation to improve cancer immunotherapy. The lead product detects active Granzyme B... using non-invasive, whole-body PET imaging combined with targeted radiotherapy."
-Sources: https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "The trial will compare this new imaging method, which targets a protein called Granzyme B (GZMB), with the current standard imaging technique, 18F-FDG PET/CT."
-Sources: https://clinconnect.io/trials/NCT06916442</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "CytoSite Bio has developed and validated the first and only commercial clinical PET agent to detect and quantify T cell and NK cell activation for investigative use. Our products detect active Granzyme B... using non-invasive, whole-body PET imaging."
-Sources: https://www.cytositebio.com</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "This clinical trial is studying a new imaging technique that uses a special marker to help doctors monitor how well immunotherapy is working for patients with advanced solid tumors... The trial will compare this new imaging method, which targets a protein called Granzyme B (GZMB), with the current standard imaging technique, 18F-FDG PET/CT."
-Sources: https://clinconnect.io/trials/NCT06916442</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Granzyme B-targeted PET Imaging Monitoring Tumor Responses to Immunotherapy. Launched by ZHONGNAN HOSPITAL · Mar 31, 2025"
-Sources: https://clinconnect.io/trials/NCT06916442</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "This strategic collaboration creates a clear path to commercialization with an ideal partner in the radiopharmaceutical space while providing significant value potential for CytoSite as we advance this promising technology in parallel with our own radiotherapeutic program."
-Sources: https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment, https://trialstat.com/2025/04/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment/</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "No mention of FDA or EMA designations in available sources."
-Sources: https://clinconnect.io/trials/NCT06916442, https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "Ratio Therapeutics (licensed from Merck)... CytoSite Bio Announces Agreement with Lantheus for Granzyme B Targeted PET Imaging Radiotracer for Immunotherapy Assessment."
-Sources: https://trialstat.com/2025/04/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment/, https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="8"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Quote: "The goal of our study was to use molecular imaging of immune changes to characterize obesity-induced differences in the breast cancer...
-CytoSite Bio Announces Agreement with Lantheus for Granzyme B Targeted PET Imaging Radiotracer for Immunotherapy Assessment...
-This clinical trial is studying a new imaging technique that uses a special marker to help doctors monitor how well immunotherapy is working for patients with advanced solid tumors."
-Sources: https://jnm.snmjournals.org/content/early/2025/05/29/jnumed.124.268938, https://trialstat.com/2025/04/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment/, https://clinconnect.io/trials/NCT06916442</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
+    <comment ref="D2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029000000}">
       <text>
         <r>
           <rPr>
@@ -603,7 +41,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A000000}">
       <text>
         <r>
           <rPr>
@@ -617,7 +55,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
+    <comment ref="F2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B000000}">
       <text>
         <r>
           <rPr>
@@ -631,7 +69,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C000000}">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C000000}">
       <text>
         <r>
           <rPr>
@@ -645,7 +83,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D000000}">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D000000}">
       <text>
         <r>
           <rPr>
@@ -659,7 +97,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E000000}">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E000000}">
       <text>
         <r>
           <rPr>
@@ -673,7 +111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F000000}">
+    <comment ref="J2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F000000}">
       <text>
         <r>
           <rPr>
@@ -687,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030000000}">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030000000}">
       <text>
         <r>
           <rPr>
@@ -701,7 +139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031000000}">
+    <comment ref="L2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031000000}">
       <text>
         <r>
           <rPr>
@@ -715,7 +153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032000000}">
+    <comment ref="M2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032000000}">
       <text>
         <r>
           <rPr>
@@ -729,7 +167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033000000}">
+    <comment ref="D3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033000000}">
       <text>
         <r>
           <rPr>
@@ -743,7 +181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034000000}">
+    <comment ref="E3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034000000}">
       <text>
         <r>
           <rPr>
@@ -757,7 +195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035000000}">
+    <comment ref="F3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035000000}">
       <text>
         <r>
           <rPr>
@@ -771,7 +209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036000000}">
+    <comment ref="G3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036000000}">
       <text>
         <r>
           <rPr>
@@ -785,7 +223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000037000000}">
+    <comment ref="H3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000037000000}">
       <text>
         <r>
           <rPr>
@@ -799,7 +237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000038000000}">
+    <comment ref="I3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000038000000}">
       <text>
         <r>
           <rPr>
@@ -813,7 +251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000039000000}">
+    <comment ref="J3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000039000000}">
       <text>
         <r>
           <rPr>
@@ -827,7 +265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003A000000}">
+    <comment ref="K3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003A000000}">
       <text>
         <r>
           <rPr>
@@ -841,7 +279,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003B000000}">
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003B000000}">
       <text>
         <r>
           <rPr>
@@ -855,7 +293,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003C000000}">
+    <comment ref="M3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003C000000}">
       <text>
         <r>
           <rPr>
@@ -870,7 +308,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003D000000}">
+    <comment ref="D4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003D000000}">
       <text>
         <r>
           <rPr>
@@ -884,7 +322,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003E000000}">
+    <comment ref="E4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003E000000}">
       <text>
         <r>
           <rPr>
@@ -898,7 +336,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003F000000}">
+    <comment ref="F4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003F000000}">
       <text>
         <r>
           <rPr>
@@ -912,7 +350,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000040000000}">
+    <comment ref="G4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000040000000}">
       <text>
         <r>
           <rPr>
@@ -926,7 +364,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000041000000}">
+    <comment ref="H4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000041000000}">
       <text>
         <r>
           <rPr>
@@ -940,7 +378,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000042000000}">
+    <comment ref="I4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000042000000}">
       <text>
         <r>
           <rPr>
@@ -954,7 +392,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000043000000}">
+    <comment ref="J4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000043000000}">
       <text>
         <r>
           <rPr>
@@ -968,7 +406,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000044000000}">
+    <comment ref="K4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000044000000}">
       <text>
         <r>
           <rPr>
@@ -982,7 +420,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000045000000}">
+    <comment ref="L4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000045000000}">
       <text>
         <r>
           <rPr>
@@ -996,7 +434,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000046000000}">
+    <comment ref="M4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000046000000}">
       <text>
         <r>
           <rPr>
@@ -1014,7 +452,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000047000000}">
+    <comment ref="D5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000047000000}">
       <text>
         <r>
           <rPr>
@@ -1028,7 +466,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000048000000}">
+    <comment ref="E5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000048000000}">
       <text>
         <r>
           <rPr>
@@ -1042,7 +480,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000049000000}">
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000049000000}">
       <text>
         <r>
           <rPr>
@@ -1056,7 +494,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004A000000}">
+    <comment ref="G5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004A000000}">
       <text>
         <r>
           <rPr>
@@ -1070,7 +508,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004B000000}">
+    <comment ref="H5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004B000000}">
       <text>
         <r>
           <rPr>
@@ -1084,7 +522,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004C000000}">
+    <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004C000000}">
       <text>
         <r>
           <rPr>
@@ -1098,7 +536,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004D000000}">
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004D000000}">
       <text>
         <r>
           <rPr>
@@ -1112,7 +550,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004E000000}">
+    <comment ref="K5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004E000000}">
       <text>
         <r>
           <rPr>
@@ -1126,7 +564,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004F000000}">
+    <comment ref="L5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004F000000}">
       <text>
         <r>
           <rPr>
@@ -1140,7 +578,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000050000000}">
+    <comment ref="M5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000050000000}">
       <text>
         <r>
           <rPr>
@@ -1154,7 +592,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000051000000}">
+    <comment ref="D6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000051000000}">
       <text>
         <r>
           <rPr>
@@ -1168,7 +606,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000052000000}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000052000000}">
       <text>
         <r>
           <rPr>
@@ -1182,7 +620,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000053000000}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000053000000}">
       <text>
         <r>
           <rPr>
@@ -1196,7 +634,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000054000000}">
+    <comment ref="G6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000054000000}">
       <text>
         <r>
           <rPr>
@@ -1210,7 +648,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000055000000}">
+    <comment ref="H6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000055000000}">
       <text>
         <r>
           <rPr>
@@ -1224,7 +662,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000056000000}">
+    <comment ref="I6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000056000000}">
       <text>
         <r>
           <rPr>
@@ -1238,7 +676,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000057000000}">
+    <comment ref="J6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000057000000}">
       <text>
         <r>
           <rPr>
@@ -1252,7 +690,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000058000000}">
+    <comment ref="K6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000058000000}">
       <text>
         <r>
           <rPr>
@@ -1266,7 +704,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000059000000}">
+    <comment ref="L6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000059000000}">
       <text>
         <r>
           <rPr>
@@ -1280,7 +718,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005A000000}">
+    <comment ref="M6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005A000000}">
       <text>
         <r>
           <rPr>
@@ -1296,7 +734,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005B000000}">
+    <comment ref="D7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005B000000}">
       <text>
         <r>
           <rPr>
@@ -1310,7 +748,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005C000000}">
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005C000000}">
       <text>
         <r>
           <rPr>
@@ -1324,7 +762,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005D000000}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005D000000}">
       <text>
         <r>
           <rPr>
@@ -1338,7 +776,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005E000000}">
+    <comment ref="G7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005E000000}">
       <text>
         <r>
           <rPr>
@@ -1352,7 +790,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005F000000}">
+    <comment ref="H7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00005F000000}">
       <text>
         <r>
           <rPr>
@@ -1366,7 +804,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000060000000}">
+    <comment ref="I7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000060000000}">
       <text>
         <r>
           <rPr>
@@ -1380,7 +818,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000061000000}">
+    <comment ref="J7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000061000000}">
       <text>
         <r>
           <rPr>
@@ -1394,7 +832,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000062000000}">
+    <comment ref="K7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000062000000}">
       <text>
         <r>
           <rPr>
@@ -1408,7 +846,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000063000000}">
+    <comment ref="L7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000063000000}">
       <text>
         <r>
           <rPr>
@@ -1422,7 +860,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000064000000}">
+    <comment ref="M7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000064000000}">
       <text>
         <r>
           <rPr>
@@ -1436,7 +874,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000065000000}">
+    <comment ref="D8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000065000000}">
       <text>
         <r>
           <rPr>
@@ -1450,7 +888,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000066000000}">
+    <comment ref="E8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000066000000}">
       <text>
         <r>
           <rPr>
@@ -1464,7 +902,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000067000000}">
+    <comment ref="F8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000067000000}">
       <text>
         <r>
           <rPr>
@@ -1478,7 +916,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000068000000}">
+    <comment ref="G8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000068000000}">
       <text>
         <r>
           <rPr>
@@ -1492,7 +930,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000069000000}">
+    <comment ref="H8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000069000000}">
       <text>
         <r>
           <rPr>
@@ -1506,7 +944,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006A000000}">
+    <comment ref="I8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006A000000}">
       <text>
         <r>
           <rPr>
@@ -1520,7 +958,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006B000000}">
+    <comment ref="J8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006B000000}">
       <text>
         <r>
           <rPr>
@@ -1534,7 +972,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006C000000}">
+    <comment ref="K8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006C000000}">
       <text>
         <r>
           <rPr>
@@ -1548,7 +986,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006D000000}">
+    <comment ref="L8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006D000000}">
       <text>
         <r>
           <rPr>
@@ -1562,7 +1000,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006E000000}">
+    <comment ref="M8" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006E000000}">
       <text>
         <r>
           <rPr>
@@ -1578,7 +1016,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006F000000}">
+    <comment ref="D9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00006F000000}">
       <text>
         <r>
           <rPr>
@@ -1592,7 +1030,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000070000000}">
+    <comment ref="E9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000070000000}">
       <text>
         <r>
           <rPr>
@@ -1606,7 +1044,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000071000000}">
+    <comment ref="F9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000071000000}">
       <text>
         <r>
           <rPr>
@@ -1620,7 +1058,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000072000000}">
+    <comment ref="G9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000072000000}">
       <text>
         <r>
           <rPr>
@@ -1634,7 +1072,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000073000000}">
+    <comment ref="H9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000073000000}">
       <text>
         <r>
           <rPr>
@@ -1648,7 +1086,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000074000000}">
+    <comment ref="I9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000074000000}">
       <text>
         <r>
           <rPr>
@@ -1662,7 +1100,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000075000000}">
+    <comment ref="J9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000075000000}">
       <text>
         <r>
           <rPr>
@@ -1676,7 +1114,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000076000000}">
+    <comment ref="K9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000076000000}">
       <text>
         <r>
           <rPr>
@@ -1690,7 +1128,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000077000000}">
+    <comment ref="L9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000077000000}">
       <text>
         <r>
           <rPr>
@@ -1704,7 +1142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000078000000}">
+    <comment ref="M9" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000078000000}">
       <text>
         <r>
           <rPr>
@@ -1720,7 +1158,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000079000000}">
+    <comment ref="D10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000079000000}">
       <text>
         <r>
           <rPr>
@@ -1734,7 +1172,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007A000000}">
+    <comment ref="E10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007A000000}">
       <text>
         <r>
           <rPr>
@@ -1748,7 +1186,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007B000000}">
+    <comment ref="F10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007B000000}">
       <text>
         <r>
           <rPr>
@@ -1762,7 +1200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007C000000}">
+    <comment ref="G10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007C000000}">
       <text>
         <r>
           <rPr>
@@ -1776,7 +1214,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007D000000}">
+    <comment ref="H10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007D000000}">
       <text>
         <r>
           <rPr>
@@ -1790,7 +1228,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007E000000}">
+    <comment ref="I10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007E000000}">
       <text>
         <r>
           <rPr>
@@ -1804,7 +1242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007F000000}">
+    <comment ref="J10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00007F000000}">
       <text>
         <r>
           <rPr>
@@ -1818,7 +1256,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000080000000}">
+    <comment ref="K10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000080000000}">
       <text>
         <r>
           <rPr>
@@ -1832,7 +1270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000081000000}">
+    <comment ref="L10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000081000000}">
       <text>
         <r>
           <rPr>
@@ -1846,7 +1284,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000082000000}">
+    <comment ref="M10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000082000000}">
       <text>
         <r>
           <rPr>
@@ -1863,7 +1301,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000083000000}">
+    <comment ref="D11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000083000000}">
       <text>
         <r>
           <rPr>
@@ -1877,7 +1315,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000084000000}">
+    <comment ref="E11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000084000000}">
       <text>
         <r>
           <rPr>
@@ -1891,7 +1329,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000085000000}">
+    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000085000000}">
       <text>
         <r>
           <rPr>
@@ -1905,7 +1343,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000086000000}">
+    <comment ref="G11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000086000000}">
       <text>
         <r>
           <rPr>
@@ -1919,7 +1357,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000087000000}">
+    <comment ref="H11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000087000000}">
       <text>
         <r>
           <rPr>
@@ -1933,7 +1371,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000088000000}">
+    <comment ref="I11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000088000000}">
       <text>
         <r>
           <rPr>
@@ -1947,7 +1385,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000089000000}">
+    <comment ref="J11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000089000000}">
       <text>
         <r>
           <rPr>
@@ -1961,7 +1399,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008A000000}">
+    <comment ref="K11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008A000000}">
       <text>
         <r>
           <rPr>
@@ -1975,7 +1413,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008B000000}">
+    <comment ref="L11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008B000000}">
       <text>
         <r>
           <rPr>
@@ -1989,7 +1427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008C000000}">
+    <comment ref="M11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008C000000}">
       <text>
         <r>
           <rPr>
@@ -2005,7 +1443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008D000000}">
+    <comment ref="D12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008D000000}">
       <text>
         <r>
           <rPr>
@@ -2019,7 +1457,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008E000000}">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008E000000}">
       <text>
         <r>
           <rPr>
@@ -2033,7 +1471,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008F000000}">
+    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00008F000000}">
       <text>
         <r>
           <rPr>
@@ -2047,7 +1485,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000090000000}">
+    <comment ref="G12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000090000000}">
       <text>
         <r>
           <rPr>
@@ -2061,7 +1499,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000091000000}">
+    <comment ref="H12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000091000000}">
       <text>
         <r>
           <rPr>
@@ -2075,7 +1513,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000092000000}">
+    <comment ref="I12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000092000000}">
       <text>
         <r>
           <rPr>
@@ -2089,7 +1527,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000093000000}">
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000093000000}">
       <text>
         <r>
           <rPr>
@@ -2103,7 +1541,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000094000000}">
+    <comment ref="K12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000094000000}">
       <text>
         <r>
           <rPr>
@@ -2117,7 +1555,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000095000000}">
+    <comment ref="L12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000095000000}">
       <text>
         <r>
           <rPr>
@@ -2131,7 +1569,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000096000000}">
+    <comment ref="M12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000096000000}">
       <text>
         <r>
           <rPr>
@@ -2149,7 +1587,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000097000000}">
+    <comment ref="D13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000097000000}">
       <text>
         <r>
           <rPr>
@@ -2163,7 +1601,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000098000000}">
+    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000098000000}">
       <text>
         <r>
           <rPr>
@@ -2177,7 +1615,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000099000000}">
+    <comment ref="F13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000099000000}">
       <text>
         <r>
           <rPr>
@@ -2191,7 +1629,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009A000000}">
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009A000000}">
       <text>
         <r>
           <rPr>
@@ -2205,7 +1643,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009B000000}">
+    <comment ref="H13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009B000000}">
       <text>
         <r>
           <rPr>
@@ -2219,7 +1657,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009C000000}">
+    <comment ref="I13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009C000000}">
       <text>
         <r>
           <rPr>
@@ -2233,7 +1671,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009D000000}">
+    <comment ref="J13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009D000000}">
       <text>
         <r>
           <rPr>
@@ -2247,7 +1685,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009E000000}">
+    <comment ref="K13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009E000000}">
       <text>
         <r>
           <rPr>
@@ -2261,7 +1699,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009F000000}">
+    <comment ref="L13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00009F000000}">
       <text>
         <r>
           <rPr>
@@ -2275,7 +1713,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A0000000}">
+    <comment ref="M13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A0000000}">
       <text>
         <r>
           <rPr>
@@ -2289,7 +1727,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A1000000}">
+    <comment ref="D14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A1000000}">
       <text>
         <r>
           <rPr>
@@ -2303,7 +1741,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A2000000}">
+    <comment ref="E14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A2000000}">
       <text>
         <r>
           <rPr>
@@ -2317,7 +1755,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A3000000}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A3000000}">
       <text>
         <r>
           <rPr>
@@ -2331,7 +1769,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A4000000}">
+    <comment ref="G14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A4000000}">
       <text>
         <r>
           <rPr>
@@ -2345,7 +1783,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A5000000}">
+    <comment ref="H14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A5000000}">
       <text>
         <r>
           <rPr>
@@ -2359,7 +1797,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A6000000}">
+    <comment ref="I14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A6000000}">
       <text>
         <r>
           <rPr>
@@ -2373,7 +1811,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A7000000}">
+    <comment ref="J14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A7000000}">
       <text>
         <r>
           <rPr>
@@ -2387,7 +1825,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A8000000}">
+    <comment ref="K14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A8000000}">
       <text>
         <r>
           <rPr>
@@ -2401,7 +1839,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A9000000}">
+    <comment ref="L14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000A9000000}">
       <text>
         <r>
           <rPr>
@@ -2415,7 +1853,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AA000000}">
+    <comment ref="M14" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AA000000}">
       <text>
         <r>
           <rPr>
@@ -2429,7 +1867,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AB000000}">
+    <comment ref="D15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AB000000}">
       <text>
         <r>
           <rPr>
@@ -2443,7 +1881,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AC000000}">
+    <comment ref="E15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AC000000}">
       <text>
         <r>
           <rPr>
@@ -2457,7 +1895,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AD000000}">
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AD000000}">
       <text>
         <r>
           <rPr>
@@ -2471,7 +1909,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AE000000}">
+    <comment ref="G15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AE000000}">
       <text>
         <r>
           <rPr>
@@ -2485,7 +1923,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AF000000}">
+    <comment ref="H15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000AF000000}">
       <text>
         <r>
           <rPr>
@@ -2499,7 +1937,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B0000000}">
+    <comment ref="I15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B0000000}">
       <text>
         <r>
           <rPr>
@@ -2513,7 +1951,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B1000000}">
+    <comment ref="J15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B1000000}">
       <text>
         <r>
           <rPr>
@@ -2527,7 +1965,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B2000000}">
+    <comment ref="K15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B2000000}">
       <text>
         <r>
           <rPr>
@@ -2541,7 +1979,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B3000000}">
+    <comment ref="L15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B3000000}">
       <text>
         <r>
           <rPr>
@@ -2555,7 +1993,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B4000000}">
+    <comment ref="M15" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B4000000}">
       <text>
         <r>
           <rPr>
@@ -2569,7 +2007,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B5000000}">
+    <comment ref="D16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B5000000}">
       <text>
         <r>
           <rPr>
@@ -2583,7 +2021,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B6000000}">
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B6000000}">
       <text>
         <r>
           <rPr>
@@ -2597,7 +2035,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B7000000}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B7000000}">
       <text>
         <r>
           <rPr>
@@ -2611,7 +2049,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B8000000}">
+    <comment ref="G16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B8000000}">
       <text>
         <r>
           <rPr>
@@ -2625,7 +2063,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B9000000}">
+    <comment ref="H16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000B9000000}">
       <text>
         <r>
           <rPr>
@@ -2639,7 +2077,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BA000000}">
+    <comment ref="I16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BA000000}">
       <text>
         <r>
           <rPr>
@@ -2653,7 +2091,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BB000000}">
+    <comment ref="J16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BB000000}">
       <text>
         <r>
           <rPr>
@@ -2667,7 +2105,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BC000000}">
+    <comment ref="K16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BC000000}">
       <text>
         <r>
           <rPr>
@@ -2681,7 +2119,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BD000000}">
+    <comment ref="L16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BD000000}">
       <text>
         <r>
           <rPr>
@@ -2695,7 +2133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BE000000}">
+    <comment ref="M16" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BE000000}">
       <text>
         <r>
           <rPr>
@@ -2711,7 +2149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BF000000}">
+    <comment ref="D17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000BF000000}">
       <text>
         <r>
           <rPr>
@@ -2725,7 +2163,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C0000000}">
+    <comment ref="E17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C0000000}">
       <text>
         <r>
           <rPr>
@@ -2739,7 +2177,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C1000000}">
+    <comment ref="F17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C1000000}">
       <text>
         <r>
           <rPr>
@@ -2753,7 +2191,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C2000000}">
+    <comment ref="G17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C2000000}">
       <text>
         <r>
           <rPr>
@@ -2767,7 +2205,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C3000000}">
+    <comment ref="H17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C3000000}">
       <text>
         <r>
           <rPr>
@@ -2781,7 +2219,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C4000000}">
+    <comment ref="I17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C4000000}">
       <text>
         <r>
           <rPr>
@@ -2795,7 +2233,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C5000000}">
+    <comment ref="J17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C5000000}">
       <text>
         <r>
           <rPr>
@@ -2809,7 +2247,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C6000000}">
+    <comment ref="K17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C6000000}">
       <text>
         <r>
           <rPr>
@@ -2823,7 +2261,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C7000000}">
+    <comment ref="L17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C7000000}">
       <text>
         <r>
           <rPr>
@@ -2837,7 +2275,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C8000000}">
+    <comment ref="M17" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C8000000}">
       <text>
         <r>
           <rPr>
@@ -2853,7 +2291,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C9000000}">
+    <comment ref="D18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000C9000000}">
       <text>
         <r>
           <rPr>
@@ -2867,7 +2305,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CA000000}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CA000000}">
       <text>
         <r>
           <rPr>
@@ -2881,7 +2319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CB000000}">
+    <comment ref="F18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CB000000}">
       <text>
         <r>
           <rPr>
@@ -2895,7 +2333,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CC000000}">
+    <comment ref="G18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CC000000}">
       <text>
         <r>
           <rPr>
@@ -2909,7 +2347,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CD000000}">
+    <comment ref="H18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CD000000}">
       <text>
         <r>
           <rPr>
@@ -2923,7 +2361,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CE000000}">
+    <comment ref="I18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CE000000}">
       <text>
         <r>
           <rPr>
@@ -2937,7 +2375,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CF000000}">
+    <comment ref="J18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000CF000000}">
       <text>
         <r>
           <rPr>
@@ -2951,7 +2389,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D0000000}">
+    <comment ref="K18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D0000000}">
       <text>
         <r>
           <rPr>
@@ -2965,7 +2403,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D1000000}">
+    <comment ref="L18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D1000000}">
       <text>
         <r>
           <rPr>
@@ -2979,7 +2417,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D2000000}">
+    <comment ref="M18" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D2000000}">
       <text>
         <r>
           <rPr>
@@ -2995,7 +2433,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D3000000}">
+    <comment ref="D19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D3000000}">
       <text>
         <r>
           <rPr>
@@ -3009,7 +2447,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D4000000}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D4000000}">
       <text>
         <r>
           <rPr>
@@ -3023,7 +2461,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D5000000}">
+    <comment ref="F19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D5000000}">
       <text>
         <r>
           <rPr>
@@ -3037,7 +2475,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D6000000}">
+    <comment ref="G19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D6000000}">
       <text>
         <r>
           <rPr>
@@ -3051,7 +2489,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D7000000}">
+    <comment ref="H19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D7000000}">
       <text>
         <r>
           <rPr>
@@ -3065,7 +2503,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D8000000}">
+    <comment ref="I19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D8000000}">
       <text>
         <r>
           <rPr>
@@ -3079,7 +2517,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D9000000}">
+    <comment ref="J19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000D9000000}">
       <text>
         <r>
           <rPr>
@@ -3093,7 +2531,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DA000000}">
+    <comment ref="K19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DA000000}">
       <text>
         <r>
           <rPr>
@@ -3107,7 +2545,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DB000000}">
+    <comment ref="L19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DB000000}">
       <text>
         <r>
           <rPr>
@@ -3121,7 +2559,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DC000000}">
+    <comment ref="M19" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DC000000}">
       <text>
         <r>
           <rPr>
@@ -3137,7 +2575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DD000000}">
+    <comment ref="D20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DD000000}">
       <text>
         <r>
           <rPr>
@@ -3151,7 +2589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DE000000}">
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DE000000}">
       <text>
         <r>
           <rPr>
@@ -3165,7 +2603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DF000000}">
+    <comment ref="F20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000DF000000}">
       <text>
         <r>
           <rPr>
@@ -3179,7 +2617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E0000000}">
+    <comment ref="G20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E0000000}">
       <text>
         <r>
           <rPr>
@@ -3193,7 +2631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E1000000}">
+    <comment ref="H20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E1000000}">
       <text>
         <r>
           <rPr>
@@ -3207,7 +2645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E2000000}">
+    <comment ref="I20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E2000000}">
       <text>
         <r>
           <rPr>
@@ -3221,7 +2659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E3000000}">
+    <comment ref="J20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E3000000}">
       <text>
         <r>
           <rPr>
@@ -3235,7 +2673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E4000000}">
+    <comment ref="K20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E4000000}">
       <text>
         <r>
           <rPr>
@@ -3249,7 +2687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E5000000}">
+    <comment ref="L20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E5000000}">
       <text>
         <r>
           <rPr>
@@ -3263,7 +2701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E6000000}">
+    <comment ref="M20" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E6000000}">
       <text>
         <r>
           <rPr>
@@ -3279,7 +2717,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E7000000}">
+    <comment ref="D21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E7000000}">
       <text>
         <r>
           <rPr>
@@ -3293,7 +2731,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E8000000}">
+    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E8000000}">
       <text>
         <r>
           <rPr>
@@ -3307,7 +2745,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E9000000}">
+    <comment ref="F21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000E9000000}">
       <text>
         <r>
           <rPr>
@@ -3321,7 +2759,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EA000000}">
+    <comment ref="G21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EA000000}">
       <text>
         <r>
           <rPr>
@@ -3335,7 +2773,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EB000000}">
+    <comment ref="H21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EB000000}">
       <text>
         <r>
           <rPr>
@@ -3349,7 +2787,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EC000000}">
+    <comment ref="I21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EC000000}">
       <text>
         <r>
           <rPr>
@@ -3363,7 +2801,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000ED000000}">
+    <comment ref="J21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000ED000000}">
       <text>
         <r>
           <rPr>
@@ -3377,7 +2815,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EE000000}">
+    <comment ref="K21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EE000000}">
       <text>
         <r>
           <rPr>
@@ -3391,7 +2829,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EF000000}">
+    <comment ref="L21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000EF000000}">
       <text>
         <r>
           <rPr>
@@ -3405,7 +2843,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F0000000}">
+    <comment ref="M21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F0000000}">
       <text>
         <r>
           <rPr>
@@ -3419,7 +2857,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F1000000}">
+    <comment ref="D22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F1000000}">
       <text>
         <r>
           <rPr>
@@ -3433,7 +2871,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F2000000}">
+    <comment ref="E22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F2000000}">
       <text>
         <r>
           <rPr>
@@ -3447,7 +2885,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F3000000}">
+    <comment ref="F22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F3000000}">
       <text>
         <r>
           <rPr>
@@ -3461,7 +2899,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F4000000}">
+    <comment ref="G22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F4000000}">
       <text>
         <r>
           <rPr>
@@ -3475,7 +2913,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F5000000}">
+    <comment ref="H22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F5000000}">
       <text>
         <r>
           <rPr>
@@ -3489,7 +2927,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F6000000}">
+    <comment ref="I22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F6000000}">
       <text>
         <r>
           <rPr>
@@ -3503,7 +2941,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F7000000}">
+    <comment ref="J22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F7000000}">
       <text>
         <r>
           <rPr>
@@ -3517,7 +2955,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F8000000}">
+    <comment ref="K22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F8000000}">
       <text>
         <r>
           <rPr>
@@ -3531,7 +2969,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F9000000}">
+    <comment ref="L22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000F9000000}">
       <text>
         <r>
           <rPr>
@@ -3545,7 +2983,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FA000000}">
+    <comment ref="M22" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FA000000}">
       <text>
         <r>
           <rPr>
@@ -3561,7 +2999,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FB000000}">
+    <comment ref="D23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FB000000}">
       <text>
         <r>
           <rPr>
@@ -3575,7 +3013,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FC000000}">
+    <comment ref="E23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FC000000}">
       <text>
         <r>
           <rPr>
@@ -3589,7 +3027,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FD000000}">
+    <comment ref="F23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FD000000}">
       <text>
         <r>
           <rPr>
@@ -3603,7 +3041,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FE000000}">
+    <comment ref="G23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FE000000}">
       <text>
         <r>
           <rPr>
@@ -3617,7 +3055,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FF000000}">
+    <comment ref="H23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-0000FF000000}">
       <text>
         <r>
           <rPr>
@@ -3631,7 +3069,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000000010000}">
+    <comment ref="I23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000000010000}">
       <text>
         <r>
           <rPr>
@@ -3645,7 +3083,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001010000}">
+    <comment ref="J23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001010000}">
       <text>
         <r>
           <rPr>
@@ -3659,7 +3097,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002010000}">
+    <comment ref="K23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002010000}">
       <text>
         <r>
           <rPr>
@@ -3673,7 +3111,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003010000}">
+    <comment ref="L23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003010000}">
       <text>
         <r>
           <rPr>
@@ -3687,7 +3125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004010000}">
+    <comment ref="M23" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004010000}">
       <text>
         <r>
           <rPr>
@@ -3701,7 +3139,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005010000}">
+    <comment ref="D24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005010000}">
       <text>
         <r>
           <rPr>
@@ -3715,7 +3153,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006010000}">
+    <comment ref="E24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006010000}">
       <text>
         <r>
           <rPr>
@@ -3729,7 +3167,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007010000}">
+    <comment ref="F24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007010000}">
       <text>
         <r>
           <rPr>
@@ -3743,7 +3181,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008010000}">
+    <comment ref="G24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008010000}">
       <text>
         <r>
           <rPr>
@@ -3757,7 +3195,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009010000}">
+    <comment ref="H24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009010000}">
       <text>
         <r>
           <rPr>
@@ -3771,7 +3209,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A010000}">
+    <comment ref="I24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A010000}">
       <text>
         <r>
           <rPr>
@@ -3785,7 +3223,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B010000}">
+    <comment ref="J24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B010000}">
       <text>
         <r>
           <rPr>
@@ -3799,7 +3237,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C010000}">
+    <comment ref="K24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C010000}">
       <text>
         <r>
           <rPr>
@@ -3813,7 +3251,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D010000}">
+    <comment ref="L24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D010000}">
       <text>
         <r>
           <rPr>
@@ -3827,7 +3265,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E010000}">
+    <comment ref="M24" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E010000}">
       <text>
         <r>
           <rPr>
@@ -3843,7 +3281,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F010000}">
+    <comment ref="D25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F010000}">
       <text>
         <r>
           <rPr>
@@ -3857,7 +3295,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010010000}">
+    <comment ref="E25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010010000}">
       <text>
         <r>
           <rPr>
@@ -3871,7 +3309,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011010000}">
+    <comment ref="F25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011010000}">
       <text>
         <r>
           <rPr>
@@ -3885,7 +3323,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012010000}">
+    <comment ref="G25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012010000}">
       <text>
         <r>
           <rPr>
@@ -3899,7 +3337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013010000}">
+    <comment ref="H25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013010000}">
       <text>
         <r>
           <rPr>
@@ -3913,7 +3351,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014010000}">
+    <comment ref="I25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014010000}">
       <text>
         <r>
           <rPr>
@@ -3927,7 +3365,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015010000}">
+    <comment ref="J25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015010000}">
       <text>
         <r>
           <rPr>
@@ -3941,7 +3379,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016010000}">
+    <comment ref="K25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016010000}">
       <text>
         <r>
           <rPr>
@@ -3955,7 +3393,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017010000}">
+    <comment ref="L25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017010000}">
       <text>
         <r>
           <rPr>
@@ -3969,7 +3407,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018010000}">
+    <comment ref="M25" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018010000}">
       <text>
         <r>
           <rPr>
@@ -3983,7 +3421,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019010000}">
+    <comment ref="D26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019010000}">
       <text>
         <r>
           <rPr>
@@ -3997,7 +3435,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A010000}">
+    <comment ref="E26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A010000}">
       <text>
         <r>
           <rPr>
@@ -4011,7 +3449,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B010000}">
+    <comment ref="F26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B010000}">
       <text>
         <r>
           <rPr>
@@ -4025,7 +3463,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C010000}">
+    <comment ref="G26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C010000}">
       <text>
         <r>
           <rPr>
@@ -4039,7 +3477,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D010000}">
+    <comment ref="H26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D010000}">
       <text>
         <r>
           <rPr>
@@ -4053,7 +3491,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E010000}">
+    <comment ref="I26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E010000}">
       <text>
         <r>
           <rPr>
@@ -4067,7 +3505,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F010000}">
+    <comment ref="J26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F010000}">
       <text>
         <r>
           <rPr>
@@ -4081,7 +3519,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020010000}">
+    <comment ref="K26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020010000}">
       <text>
         <r>
           <rPr>
@@ -4095,7 +3533,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021010000}">
+    <comment ref="L26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021010000}">
       <text>
         <r>
           <rPr>
@@ -4109,7 +3547,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022010000}">
+    <comment ref="M26" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022010000}">
       <text>
         <r>
           <rPr>
@@ -4123,7 +3561,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023010000}">
+    <comment ref="D27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023010000}">
       <text>
         <r>
           <rPr>
@@ -4137,7 +3575,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024010000}">
+    <comment ref="E27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024010000}">
       <text>
         <r>
           <rPr>
@@ -4151,7 +3589,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025010000}">
+    <comment ref="F27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025010000}">
       <text>
         <r>
           <rPr>
@@ -4165,7 +3603,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026010000}">
+    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026010000}">
       <text>
         <r>
           <rPr>
@@ -4179,7 +3617,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027010000}">
+    <comment ref="H27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027010000}">
       <text>
         <r>
           <rPr>
@@ -4193,7 +3631,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028010000}">
+    <comment ref="I27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028010000}">
       <text>
         <r>
           <rPr>
@@ -4207,7 +3645,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029010000}">
+    <comment ref="J27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000029010000}">
       <text>
         <r>
           <rPr>
@@ -4221,7 +3659,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A010000}">
+    <comment ref="K27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002A010000}">
       <text>
         <r>
           <rPr>
@@ -4235,7 +3673,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B010000}">
+    <comment ref="L27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002B010000}">
       <text>
         <r>
           <rPr>
@@ -4249,7 +3687,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C010000}">
+    <comment ref="M27" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002C010000}">
       <text>
         <r>
           <rPr>
@@ -4263,7 +3701,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D010000}">
+    <comment ref="D28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002D010000}">
       <text>
         <r>
           <rPr>
@@ -4277,7 +3715,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E010000}">
+    <comment ref="E28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002E010000}">
       <text>
         <r>
           <rPr>
@@ -4291,7 +3729,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F010000}">
+    <comment ref="F28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00002F010000}">
       <text>
         <r>
           <rPr>
@@ -4305,7 +3743,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030010000}">
+    <comment ref="G28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000030010000}">
       <text>
         <r>
           <rPr>
@@ -4319,7 +3757,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031010000}">
+    <comment ref="H28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000031010000}">
       <text>
         <r>
           <rPr>
@@ -4333,7 +3771,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032010000}">
+    <comment ref="I28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000032010000}">
       <text>
         <r>
           <rPr>
@@ -4347,7 +3785,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033010000}">
+    <comment ref="J28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000033010000}">
       <text>
         <r>
           <rPr>
@@ -4361,7 +3799,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034010000}">
+    <comment ref="K28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000034010000}">
       <text>
         <r>
           <rPr>
@@ -4375,7 +3813,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035010000}">
+    <comment ref="L28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000035010000}">
       <text>
         <r>
           <rPr>
@@ -4389,7 +3827,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036010000}">
+    <comment ref="M28" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000036010000}">
       <text>
         <r>
           <rPr>
@@ -4404,7 +3842,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000037010000}">
+    <comment ref="D29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000037010000}">
       <text>
         <r>
           <rPr>
@@ -4418,7 +3856,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000038010000}">
+    <comment ref="E29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000038010000}">
       <text>
         <r>
           <rPr>
@@ -4432,7 +3870,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000039010000}">
+    <comment ref="F29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000039010000}">
       <text>
         <r>
           <rPr>
@@ -4446,7 +3884,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003A010000}">
+    <comment ref="G29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003A010000}">
       <text>
         <r>
           <rPr>
@@ -4460,7 +3898,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003B010000}">
+    <comment ref="H29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003B010000}">
       <text>
         <r>
           <rPr>
@@ -4474,7 +3912,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003C010000}">
+    <comment ref="I29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003C010000}">
       <text>
         <r>
           <rPr>
@@ -4488,7 +3926,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003D010000}">
+    <comment ref="J29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003D010000}">
       <text>
         <r>
           <rPr>
@@ -4502,7 +3940,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003E010000}">
+    <comment ref="K29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003E010000}">
       <text>
         <r>
           <rPr>
@@ -4516,7 +3954,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003F010000}">
+    <comment ref="L29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00003F010000}">
       <text>
         <r>
           <rPr>
@@ -4530,7 +3968,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000040010000}">
+    <comment ref="M29" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000040010000}">
       <text>
         <r>
           <rPr>
@@ -4546,7 +3984,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000041010000}">
+    <comment ref="D30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000041010000}">
       <text>
         <r>
           <rPr>
@@ -4560,7 +3998,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000042010000}">
+    <comment ref="E30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000042010000}">
       <text>
         <r>
           <rPr>
@@ -4574,7 +4012,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000043010000}">
+    <comment ref="F30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000043010000}">
       <text>
         <r>
           <rPr>
@@ -4588,7 +4026,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000044010000}">
+    <comment ref="G30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000044010000}">
       <text>
         <r>
           <rPr>
@@ -4602,7 +4040,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000045010000}">
+    <comment ref="H30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000045010000}">
       <text>
         <r>
           <rPr>
@@ -4616,7 +4054,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000046010000}">
+    <comment ref="I30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000046010000}">
       <text>
         <r>
           <rPr>
@@ -4630,7 +4068,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000047010000}">
+    <comment ref="J30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000047010000}">
       <text>
         <r>
           <rPr>
@@ -4644,7 +4082,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000048010000}">
+    <comment ref="K30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000048010000}">
       <text>
         <r>
           <rPr>
@@ -4658,7 +4096,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000049010000}">
+    <comment ref="L30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000049010000}">
       <text>
         <r>
           <rPr>
@@ -4672,7 +4110,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004A010000}">
+    <comment ref="M30" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004A010000}">
       <text>
         <r>
           <rPr>
@@ -4688,7 +4126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004B010000}">
+    <comment ref="D31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004B010000}">
       <text>
         <r>
           <rPr>
@@ -4702,7 +4140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004C010000}">
+    <comment ref="E31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004C010000}">
       <text>
         <r>
           <rPr>
@@ -4716,7 +4154,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004D010000}">
+    <comment ref="F31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004D010000}">
       <text>
         <r>
           <rPr>
@@ -4730,7 +4168,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004E010000}">
+    <comment ref="G31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004E010000}">
       <text>
         <r>
           <rPr>
@@ -4744,7 +4182,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004F010000}">
+    <comment ref="H31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00004F010000}">
       <text>
         <r>
           <rPr>
@@ -4758,7 +4196,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000050010000}">
+    <comment ref="I31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000050010000}">
       <text>
         <r>
           <rPr>
@@ -4772,7 +4210,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000051010000}">
+    <comment ref="J31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000051010000}">
       <text>
         <r>
           <rPr>
@@ -4786,7 +4224,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000052010000}">
+    <comment ref="K31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000052010000}">
       <text>
         <r>
           <rPr>
@@ -4800,7 +4238,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000053010000}">
+    <comment ref="L31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000053010000}">
       <text>
         <r>
           <rPr>
@@ -4814,7 +4252,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000054010000}">
+    <comment ref="M31" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000054010000}">
       <text>
         <r>
           <rPr>
@@ -4826,6 +4264,568 @@
           <t>Quote: "Development of ²¹²Pb-based Radio-DARPin in therapy (RDT) for the treatment of mesothelin (MSLN)-positive solid tumors. Read the article.
 Monoclonal antibodies can transport and deliver radioactive elements capable of releasing sufficient amounts of energy to destroy tumor cells. In this clinical trial, we will study alpha particle radio immunotherapy using lead-212 (²¹²Pb), an isotope with a short path length targeted to malignant cells by the trastuzumab antibody, as a potential treatment for metastatic diseases. This Phase I trial is designed to determine the toxicity profile of ²¹²Pb-TCMC-Trastuzumab, its dose-limiting toxicities, and its anti-tumor effects in patients with HER-2 positive intraperitoneal cancers."
 Sources: https://www.oranomed.com/en/orano-med-ressources/publications, https://www.npcf.us/clinical-trials/safety-study-of-%C2%B2%C2%B9%C2%B2pb-tcmc-trastuzumab-radio-immunotherapy/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Cancer-associated fibroblasts selectively expressing FAP comprise up to 90% of the tumor mass in highly desmoplastic cancers, including pancreatic, breast, and colorectal. RTX-1363S has the potential to transform the way we detect and monitor various epithelial-derived cancers."
+Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.cancer.gov/about-cancer/treatment/clinical-trials/search/v?id=NCI-2025-01031, https://jnm.snmjournals.org/content/66/supplement_1/251890</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "RTX-1363S is a highly selective, high affinity FAP inhibitor that will be radiolabeled with copper-64 (Cu-64), a positron-emitting radionuclide with a half-life of 12.7 hr."
+Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "RTX-1363S is a highly selective, high affinity FAP inhibitor that will be radiolabeled with copper-64 (Cu-64), a positron-emitting radionuclide with a half-life of 12.7 hr."
+Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "RTX-1363S is a highly selective, high affinity FAP inhibitor that will be radiolabeled with copper-64 (Cu-64), a positron-emitting radionuclide with a half-life of 12.7 hr."
+Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "This is a multicenter, open-label, prospective Phase 1/2a study to assess safety and tolerability, establish dosimetry and to identify an optimal imaging dose."
+Sources: https://www.cancer.gov/about-cancer/treatment/clinical-trials/search/v?id=NCI-2025-01031</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "This is a multicenter, open-label, prospective Phase 1/2a study to assess safety and tolerability, establish dosimetry and to identify an optimal imaging dose."
+Sources: https://www.cancer.gov/about-cancer/treatment/clinical-trials/search/v?id=NCI-2025-01031</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000007000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "The study's results will guide further development of [Cu-64]-labeled RTX-1363S as a FAP-targeted tumor imaging agent."
+Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000008000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "No mention of FDA or EMA designations in available sources."
+Sources: https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial, https://jnm.snmjournals.org/content/65/supplement_2/241693</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000009000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio Therapeutics, in collaboration with Lantheus and PharmaLogic, has dosed the first patient in a phase I study investigating a novel fibroblast activated protein inhibitor (FAPI)-targeted radiopharmaceutical for PET imaging."
+Sources: https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M32" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio, in collaboration with Lantheus and PharmaLogic, is currently conducting a Phase I trial evaluating the efficacy of a novel FAP-targeted imaging biomarker, copper-64[Cu-64]-labeled LNTH-1363S (formerly RTX-1363S) for PET imaging in adult healthy volunteers. The company also recently announced a $50M Series B financing which will significantly drive the clinical advancement of Ratio’s first FAP-targeted therapeutic candidate into clinical trials this year."
+Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/, https://ratiotx.com/press-release-phase-i-novel-fap-targeted-radiopharmaceutical/, https://www.auntminnie.com/clinical-news/molecular-imaging/nuclear-medicine/article/15633887/ratio-therapeutics-highlights-first-patient-treated-in-fapi-pet-trial</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio is currently advancing its lead FAP-targeted radiotherapeutic candidate for the treatment of soft tissue sarcoma, with plans to initiate clinical trials in late 2024."
+Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio is developing a technology platform to take advantage of the tumor killing power of the alpha emitter, Actinium-225."
+Sources: https://ratiotx.com/press-release-ratio-therapeutics-launches/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio, in collaboration with Lantheus and PharmaLogic, is currently conducting a Phase I trial evaluating the efficacy of a novel FAP-targeted imaging biomarker, copper-64[Cu-64]-labeled LNTH-1363S (formerly RTX-1363S) for PET imaging in adult healthy volunteers."
+Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio is currently advancing its lead FAP-targeted radiotherapeutic candidate for the treatment of soft tissue sarcoma... Ratio’s technology platform... enables the development of tunable radiopharmaceuticals for therapy and imaging."
+Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/, https://ratiotx.com/press-release-ratio-therapeutics-launches/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00000F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "A number of groups have explored 225Ac therapy at preclinical level. One study showed that the effects of treatment with 177Lu-FAPI-46 were relatively slow but lasted longer than those of 225Ac-FAPI-46... Recently, an American group has been looking at 225Ac-FAPI-46 therapy combined with immunotherapy in immunocompetent mice with sarcomas sensitive or resistant to immunotherapy."
+Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000010000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "No clinical trial identifier found for Ratio Therapeutics' FAP-α 225Ac radiotherapeutic in soft tissue sarcoma."
+Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000011000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "The list focuses on agents in pre-registration through Phase 1 and likely to reach market in 2024-2030. ... Ratio Therapeutics' FAP-α 225Ac Radiotherapeutic is in pre-clinical stage."
+Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820, https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf017/7985571</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000012000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "No public information available regarding FDA or EMA designations for Ratio Therapeutics' FAP-α 225Ac Radiotherapeutic."
+Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820, https://jnm.snmjournals.org/content/66/supplement_1/251900</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000013000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "No public information available regarding key collaborators or licensees for Ratio Therapeutics' FAP-α 225Ac Radiotherapeutic."
+Sources: https://academic.oup.com/bjr/advance-article/doi/10.1093/bjr/tqaf020/8002820, https://jnm.snmjournals.org/content/66/supplement_1/251900</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000014000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio, in collaboration with Lantheus and PharmaLogic, is currently conducting a Phase I trial evaluating the efficacy of a novel FAP-targeted imaging biomarker... The company also recently announced a $50M Series B financing which will significantly drive the clinical advancement of Ratio’s first FAP-targeted therapeutic candidate into clinical trials this year."
+Sources: https://ratiotx.com/2024/03/12/march-12th-2024-ratio-announces-expansion-of-manufacturing-agreement-with-pharmalogic-for-fap-targeted-radiopharmaceuticals/, https://ratiotx.com/press-release-ratio-therapeutics-launches/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000015000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Together, we aim to develop a best-in-class therapy in the fight against SSTR2-expressing tumors."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000016000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000017000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000018000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio Therapeutics has inked an exclusive worldwide agreement potentially worth $745M with Novartis Pharma AG. The collaboration leverages Ratio’s radioligand therapy discovery and development expertise as well as its technology platforms for the development of a Somatostatin Receptor 2 (SSTR2) radiotherapeutic candidate for cancer."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000019000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
+Sources: https://ratiotx.com/2024/11/18/november-18th-2024-ratio-enters-license-and-collaboration-agreement-with-novartis-for-sstr2-targeting-radiotherapeutic-candidate/, https://firstwordpharma.com/story/5958720</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001A000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate."
+Sources: https://ratiotx.com/2024/11/18/november-18th-2024-ratio-enters-license-and-collaboration-agreement-with-novartis-for-sstr2-targeting-radiotherapeutic-candidate/, https://firstwordpharma.com/story/5958720</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001B000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio Therapeutics has inked an exclusive worldwide agreement potentially worth $745M with Novartis Pharma AG. The collaboration leverages Ratio’s radioligand therapy discovery and development expertise as well as its technology platforms for the development of a Somatostatin Receptor 2 (SSTR2) radiotherapeutic candidate for cancer. Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate. Novartis will assume responsibility for all remaining development, manufacturing, and commercialization activities."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001C000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "No public information available regarding FDA or EMA designations for this specific SSTR2-targeted radiotherapeutic from Ratio Therapeutics/Novartis."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001D000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio Therapeutics has inked an exclusive worldwide agreement potentially worth $745M with Novartis Pharma AG. The collaboration leverages Ratio’s radioligand therapy discovery and development expertise as well as its technology platforms for the development of a Somatostatin Receptor 2 (SSTR2) radiotherapeutic candidate for cancer."
+Sources: https://www.insideprecisionmedicine.com/topics/oncology/ratio-nets-potential-750m-radioligand-cancer-deal-with-novartis/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M34" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001E000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio will collaborate with Novartis to drive preclinical activities to research and select an SSTR2-targeting development candidate. Novartis will assume responsibility for all remaining development, manufacturing, and commercialization activities. Under the terms of the agreement, Ratio will receive combined upfront and potential milestone payments up to $745m, and is eligible to receive tiered royalty payments."
+Sources: https://ratiotx.com/2024/11/18/november-18th-2024-ratio-enters-license-and-collaboration-agreement-with-novartis-for-sstr2-targeting-radiotherapeutic-candidate/, https://firstwordpharma.com/story/5958720</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-00001F000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "This clinical trial is studying a new imaging technique that uses a special marker to help doctors monitor how well immunotherapy is working for patients with advanced solid tumors... The trial will compare this new imaging method, which targets a protein called Granzyme B (GZMB), with the current standard imaging technique, 18F-FDG PET/CT."
+Sources: https://clinconnect.io/trials/NCT06916442</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000020000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "CytoSite Bio is developing novel radiopharmaceuticals that enable the quantification and modulation of immune activation to improve cancer immunotherapy. The lead product detects active Granzyme B... using non-invasive, whole-body PET imaging combined with targeted radiotherapy."
+Sources: https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000021000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "The trial will compare this new imaging method, which targets a protein called Granzyme B (GZMB), with the current standard imaging technique, 18F-FDG PET/CT."
+Sources: https://clinconnect.io/trials/NCT06916442</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000022000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "CytoSite Bio has developed and validated the first and only commercial clinical PET agent to detect and quantify T cell and NK cell activation for investigative use. Our products detect active Granzyme B... using non-invasive, whole-body PET imaging."
+Sources: https://www.cytositebio.com</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000023000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "This clinical trial is studying a new imaging technique that uses a special marker to help doctors monitor how well immunotherapy is working for patients with advanced solid tumors... The trial will compare this new imaging method, which targets a protein called Granzyme B (GZMB), with the current standard imaging technique, 18F-FDG PET/CT."
+Sources: https://clinconnect.io/trials/NCT06916442</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000024000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Granzyme B-targeted PET Imaging Monitoring Tumor Responses to Immunotherapy. Launched by ZHONGNAN HOSPITAL · Mar 31, 2025"
+Sources: https://clinconnect.io/trials/NCT06916442</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000025000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "This strategic collaboration creates a clear path to commercialization with an ideal partner in the radiopharmaceutical space while providing significant value potential for CytoSite as we advance this promising technology in parallel with our own radiotherapeutic program."
+Sources: https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment, https://trialstat.com/2025/04/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment/</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000026000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "No mention of FDA or EMA designations in available sources."
+Sources: https://clinconnect.io/trials/NCT06916442, https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="L35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000027000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "Ratio Therapeutics (licensed from Merck)... CytoSite Bio Announces Agreement with Lantheus for Granzyme B Targeted PET Imaging Radiotracer for Immunotherapy Assessment."
+Sources: https://trialstat.com/2025/04/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment/, https://www.biospace.com/press-releases/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="M35" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000028000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="8"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Quote: "The goal of our study was to use molecular imaging of immune changes to characterize obesity-induced differences in the breast cancer...
+CytoSite Bio Announces Agreement with Lantheus for Granzyme B Targeted PET Imaging Radiotracer for Immunotherapy Assessment...
+This clinical trial is studying a new imaging technique that uses a special marker to help doctors monitor how well immunotherapy is working for patients with advanced solid tumors."
+Sources: https://jnm.snmjournals.org/content/early/2025/05/29/jnumed.124.268938, https://trialstat.com/2025/04/cytosite-bio-announces-agreement-with-lantheus-for-granzyme-b-targeted-pet-imaging-radiotracer-for-immunotherapy-assessment/, https://clinconnect.io/trials/NCT06916442</t>
         </r>
       </text>
     </comment>
@@ -8801,31 +8801,31 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>19</v>
+        <v>54</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>20</v>
+        <v>55</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>22</v>
@@ -8834,162 +8834,162 @@
         <v>17</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>24</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" s="4" t="s">
         <v>17</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>63</v>
       </c>
       <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="2" t="s">
         <v>17</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>31</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>30</v>
+        <v>68</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>17</v>
+        <v>69</v>
       </c>
       <c r="J4" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>17</v>
+        <v>70</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>37</v>
+        <v>71</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>38</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="B5" t="s">
-        <v>40</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>42</v>
+        <v>75</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>77</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C6" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>22</v>
@@ -8998,109 +8998,109 @@
         <v>17</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="G7" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="M7" s="2" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="B8" t="s">
-        <v>66</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>67</v>
+        <v>100</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>17</v>
+        <v>101</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>36</v>
+        <v>102</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>69</v>
+        <v>103</v>
       </c>
       <c r="J8" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>71</v>
+        <v>104</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>72</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>106</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C9" t="s">
         <v>61</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>75</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>76</v>
+        <v>28</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>17</v>
@@ -9109,51 +9109,51 @@
         <v>36</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="L9" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="L9" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="M9" s="2" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="B10" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>61</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>83</v>
+        <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>68</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>22</v>
@@ -9162,106 +9162,106 @@
         <v>17</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>86</v>
+        <v>17</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="B11" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="C11" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="G11" s="2" t="s">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>96</v>
+        <v>22</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="L11" s="2" t="s">
+        <v>17</v>
+      </c>
       <c r="M11" s="2" t="s">
-        <v>98</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="B12" t="s">
-        <v>89</v>
+        <v>123</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>61</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>100</v>
+        <v>112</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>101</v>
+        <v>17</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>102</v>
+        <v>36</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>77</v>
+        <v>124</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>22</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="L12" s="4" t="s">
         <v>17</v>
       </c>
+      <c r="L12" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="M12" s="2" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>106</v>
+        <v>128</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
-        <v>61</v>
+        <v>130</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>107</v>
+        <v>131</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>28</v>
@@ -9270,54 +9270,54 @@
         <v>17</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>36</v>
+        <v>132</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>108</v>
+        <v>45</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>110</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B14" t="s">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>61</v>
+        <v>136</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>114</v>
+        <v>138</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>22</v>
@@ -9329,36 +9329,36 @@
         <v>17</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>115</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>116</v>
+        <v>140</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>74</v>
       </c>
       <c r="C15" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>28</v>
+        <v>76</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>119</v>
+        <v>54</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>45</v>
+        <v>142</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="J15" s="3" t="s">
         <v>22</v>
@@ -9370,62 +9370,62 @@
         <v>17</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B16" t="s">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>112</v>
+        <v>148</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>28</v>
+        <v>149</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>124</v>
+        <v>68</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>125</v>
+        <v>151</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L16" s="2" t="s">
-        <v>126</v>
+        <v>153</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>127</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="B17" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C17" t="s">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>131</v>
+        <v>157</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>28</v>
@@ -9434,54 +9434,54 @@
         <v>17</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>132</v>
+        <v>158</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>17</v>
+        <v>124</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>159</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>17</v>
+        <v>160</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>134</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>136</v>
+        <v>164</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>137</v>
+        <v>165</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>76</v>
+        <v>166</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>18</v>
+        <v>167</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>54</v>
+        <v>168</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>55</v>
+        <v>169</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>138</v>
+        <v>170</v>
       </c>
       <c r="J18" s="3" t="s">
         <v>22</v>
@@ -9489,40 +9489,40 @@
       <c r="K18" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L18" s="2" t="s">
+      <c r="L18" s="3" t="s">
         <v>17</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>139</v>
+        <v>171</v>
       </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="B19" t="s">
-        <v>74</v>
+        <v>173</v>
       </c>
       <c r="C19" t="s">
-        <v>34</v>
+        <v>174</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>141</v>
+        <v>175</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>18</v>
+        <v>28</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>54</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>142</v>
+        <v>30</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>143</v>
+        <v>17</v>
       </c>
       <c r="J19" s="3" t="s">
         <v>22</v>
@@ -9534,118 +9534,118 @@
         <v>17</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>144</v>
+        <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="B20" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="C20" t="s">
-        <v>147</v>
+        <v>34</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>148</v>
+        <v>179</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>149</v>
+        <v>180</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>150</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>17</v>
+        <v>183</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
     </row>
     <row r="21" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="B21" t="s">
-        <v>146</v>
+        <v>187</v>
       </c>
       <c r="C21" t="s">
-        <v>156</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>157</v>
+        <v>164</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>188</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="F21" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>159</v>
+      <c r="H21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K21" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="K21" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="M21" s="2" t="s">
-        <v>161</v>
+      <c r="L21" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="22" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>162</v>
+        <v>190</v>
       </c>
       <c r="B22" t="s">
-        <v>163</v>
+        <v>82</v>
       </c>
       <c r="C22" t="s">
-        <v>164</v>
+        <v>191</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>165</v>
+        <v>192</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>166</v>
+        <v>28</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>168</v>
+        <v>193</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>170</v>
+        <v>45</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>22</v>
@@ -9653,40 +9653,40 @@
       <c r="K22" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L22" s="3" t="s">
-        <v>17</v>
+      <c r="L22" s="2" t="s">
+        <v>194</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>171</v>
+        <v>195</v>
       </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>172</v>
+        <v>196</v>
       </c>
       <c r="B23" t="s">
-        <v>173</v>
+        <v>89</v>
       </c>
       <c r="C23" t="s">
-        <v>174</v>
+        <v>197</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>17</v>
+        <v>199</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>22</v>
@@ -9698,159 +9698,159 @@
         <v>17</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>176</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>177</v>
+        <v>201</v>
       </c>
       <c r="B24" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="C24" t="s">
-        <v>34</v>
+        <v>202</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>179</v>
+        <v>203</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>180</v>
+        <v>28</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>84</v>
+        <v>204</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>181</v>
+        <v>55</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>182</v>
+        <v>22</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>183</v>
+        <v>17</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>184</v>
+        <v>17</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>185</v>
+        <v>205</v>
       </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>186</v>
+        <v>206</v>
       </c>
       <c r="B25" t="s">
-        <v>187</v>
+        <v>207</v>
       </c>
       <c r="C25" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>188</v>
+        <v>34</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>208</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F25" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="K25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K25" s="4" t="s">
+      <c r="L25" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>189</v>
+      <c r="M25" s="2" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>190</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>82</v>
+        <v>178</v>
       </c>
       <c r="C26" t="s">
-        <v>191</v>
+        <v>61</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>28</v>
+        <v>180</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>194</v>
+        <v>17</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>195</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
-        <v>89</v>
+        <v>216</v>
       </c>
       <c r="C27" t="s">
-        <v>197</v>
+        <v>34</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>198</v>
+        <v>217</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>149</v>
+        <v>218</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>119</v>
+        <v>219</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>77</v>
+        <v>220</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>199</v>
+        <v>221</v>
       </c>
       <c r="J27" s="3" t="s">
         <v>22</v>
@@ -9862,36 +9862,36 @@
         <v>17</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>200</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>201</v>
+        <v>223</v>
       </c>
       <c r="B28" t="s">
         <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>202</v>
+        <v>136</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>203</v>
+        <v>224</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>28</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>17</v>
+        <v>225</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>204</v>
+        <v>54</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>17</v>
+        <v>45</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>226</v>
       </c>
       <c r="J28" s="3" t="s">
         <v>22</v>
@@ -9903,121 +9903,121 @@
         <v>17</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>205</v>
+        <v>227</v>
       </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>206</v>
+        <v>228</v>
       </c>
       <c r="B29" t="s">
-        <v>207</v>
+        <v>229</v>
       </c>
       <c r="C29" t="s">
-        <v>34</v>
+        <v>230</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>208</v>
+        <v>231</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>52</v>
+        <v>149</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>84</v>
+        <v>150</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>209</v>
+        <v>232</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="K29" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L29" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="M29" s="2" t="s">
-        <v>211</v>
+        <v>234</v>
       </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>212</v>
+        <v>235</v>
       </c>
       <c r="B30" t="s">
-        <v>178</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
         <v>61</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>213</v>
+        <v>236</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F30" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F30" s="3" t="s">
         <v>17</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="H30" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30" s="2" t="s">
+      <c r="H30" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>17</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K30" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K30" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L30" s="2" t="s">
+      <c r="L30" s="4" t="s">
         <v>17</v>
       </c>
       <c r="M30" s="2" t="s">
-        <v>214</v>
+        <v>237</v>
       </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>238</v>
       </c>
       <c r="B31" t="s">
-        <v>216</v>
+        <v>239</v>
       </c>
       <c r="C31" t="s">
-        <v>34</v>
+        <v>164</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>217</v>
+        <v>240</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>218</v>
+        <v>180</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>17</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>219</v>
+        <v>158</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>220</v>
+        <v>45</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>221</v>
+        <v>241</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>22</v>
+        <v>152</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>17</v>
@@ -10026,36 +10026,36 @@
         <v>17</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>222</v>
+        <v>242</v>
       </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>223</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>123</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>15</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>224</v>
+        <v>16</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>225</v>
+        <v>18</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>226</v>
+        <v>21</v>
       </c>
       <c r="J32" s="3" t="s">
         <v>22</v>
@@ -10064,133 +10064,133 @@
         <v>17</v>
       </c>
       <c r="L32" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>227</v>
+        <v>24</v>
       </c>
     </row>
     <row r="33" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>228</v>
+        <v>25</v>
       </c>
       <c r="B33" t="s">
-        <v>229</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
-        <v>230</v>
+        <v>15</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>231</v>
+        <v>27</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>149</v>
+        <v>28</v>
       </c>
       <c r="F33" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>17</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="J33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K33" s="2" t="s">
-        <v>233</v>
+      <c r="K33" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="L33" s="4" t="s">
         <v>17</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>234</v>
+        <v>31</v>
       </c>
     </row>
     <row r="34" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>235</v>
+        <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>89</v>
+        <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="F34" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>17</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="I34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="J34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K34" s="4" t="s">
+      <c r="K34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="L34" s="4" t="s">
-        <v>17</v>
+      <c r="L34" s="2" t="s">
+        <v>37</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>237</v>
+        <v>38</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>238</v>
+        <v>39</v>
       </c>
       <c r="B35" t="s">
-        <v>239</v>
+        <v>40</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>41</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>240</v>
+        <v>42</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="F35" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="F35" s="3" t="s">
+        <v>43</v>
+      </c>
       <c r="G35" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="H35" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H35" s="3" t="s">
         <v>45</v>
       </c>
       <c r="I35" s="2" t="s">
-        <v>241</v>
+        <v>46</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>152</v>
+        <v>22</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>242</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
